--- a/core/data/reports/liquidity_report_2025-12-01_full.xlsx
+++ b/core/data/reports/liquidity_report_2025-12-01_full.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="ГЭП-анализ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Концентрация — Активы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Концентрация — Обязательства" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00 ₽"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -55,7 +58,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +73,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,8 +129,14 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -133,9 +147,21 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сформировано: 17.05.2026 17:40 | Единица измерения: руб.</t>
+          <t>Сформировано: 28.06.2026 20:30 | Единица измерения: руб.</t>
         </is>
       </c>
     </row>
@@ -582,53 +608,53 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3760000000</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>-360000000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-360000000</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>-0.09574500000000001</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>✗ Дефицит</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6" t="n">
+      <c r="E5" s="10" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>440000000</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v/>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>✓ Профицит</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>1 день</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>✓ Профицит</t>
         </is>
@@ -646,55 +672,55 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>600000000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>✓ Профицит</t>
+        <v>1200000000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-600000000</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-160000000</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>✗ Дефицит</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>D8_30</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>8–30 дней</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>✓ Профицит</t>
+      <c r="C7" s="10" t="n">
+        <v>1920000000</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-80000000</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-240000000</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>✗ Дефицит</t>
         </is>
       </c>
     </row>
@@ -710,53 +736,53 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>3000000000</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>✓ Профицит</t>
+        <v>15320000000</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-12320000000</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-12560000000</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>-0.8041779999999999</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>✗ Дефицит</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>D91_180</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>91–180 дней</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="C9" s="10" t="n">
+        <v>92030000000</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>89630000000</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>77070000000</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>37.345833</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>✓ Профицит</t>
         </is>
@@ -774,77 +800,77 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>1920000000</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+        <v>76440000000</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-74520000000</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>2550000000</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>-0.974882</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>✗ Дефицит</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>OVER_1Y</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Свыше 1 года</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>10800000000</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>4800000000</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>7350000000</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>✓ Профицит</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>OVER_1Y</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Свыше 1 года</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>✓ Профицит</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="14" t="n">
+        <v>114470000000</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>107120000000</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>7350000000</v>
+      </c>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -854,4 +880,1124 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Концентрация — Активы | Дата отчёта: 2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Сформировано: 28.06.2026 20:30 | Топ контрагентов по доле в портфеле</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Код контрагента</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Корзина</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Сумма, руб.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Доля, %</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Доля (кумул.)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Топ-3?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CORP001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ТехноСтрой</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>91–180 дней</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>90030000000</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.78649</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.78649</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>CBR</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>ЦБ РФ</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>cbr</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Свыше 1 года</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>4000000000</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.03494</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.82143</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Свыше 1 года</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3800000000</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0332</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.8546299999999999</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>CBR</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>ЦБ РФ</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>cbr</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>До востребования</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>3400000000</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.0297</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.8843299999999999</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ЛУКОЙЛ</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Свыше 1 года</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>3000000000</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.02621</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.9105399999999999</v>
+      </c>
+      <c r="H8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Газпром</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>91–180 дней</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.9280099999999999</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CBR</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ЦБ РФ</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>cbr</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.01747</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.9454799999999999</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>ROSNFT</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Роснефть</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.9559599999999999</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Газпром</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>181–365 дней</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.96644</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.00874</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.9751799999999998</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SBER</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Сбербанк</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0.00699</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0.9821699999999999</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>181–365 дней</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>720000000</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0.00629</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.9884599999999999</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VTB</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2–7 дней</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0.00524</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0.9936999999999999</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>ALFA</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Альфа-Банк</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.9971899999999999</v>
+      </c>
+      <c r="H17" s="18" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CORP002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>АгроПром</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>320000000</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.9999899999999999</v>
+      </c>
+      <c r="H18" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Концентрация — Обязательства | Дата отчёта: 2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Сформировано: 28.06.2026 20:30 | Топ контрагентов по доле в портфеле</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Код контрагента</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Корзина</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Сумма, руб.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Доля, %</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Доля (кумул.)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Топ-3?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>181–365 дней</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>76440000000</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.7135899999999999</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.7135899999999999</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>12600000000</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.11763</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.83122</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CORP001</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ТехноСтрой</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Свыше 1 года</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6000000000</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.05601</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.88723</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Газпром</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>91–180 дней</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.9096299999999999</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>VTB</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ВТБ</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>8–30 дней</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2000000000</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.01867</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.9283</v>
+      </c>
+      <c r="H8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>PHYS001</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Физлица</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>individual</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>До востребования</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ЛУКОЙЛ</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1600000000</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.96004</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>SBER</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Сбербанк</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>2–7 дней</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.9712400000000001</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>GAZP</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Газпром</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>До востребования</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.009340000000000001</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.9805800000000001</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>ALFA</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Альфа-Банк</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>0.9880500000000001</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>LKOH</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ЛУКОЙЛ</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>До востребования</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>720000000</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0.00672</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0.99477</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>CORP001</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>ТехноСтрой</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>31–90 дней</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>320000000</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0.00299</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.9977600000000001</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CORP002</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>АгроПром</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>corporate</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>До востребования</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0.00224</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>